--- a/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>890_康乃馨红绸_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010401010209161210</v>
+        <v>0104010102091612110</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>244_繁星_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>476_酸浆果_Physalis_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>531_小南瓜_pumpkin stick_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +664,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0104010102091612110</v>
+        <v>01040101020916121101495591291050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,10 +606,100 @@
       <c r="A21" t="str">
         <v>5</v>
       </c>
+      <c r="C21" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">542_吊米 红_hanging amaranthus
+red_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>875_九星叶红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2</v>
+      </c>
+      <c r="C28" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -664,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01040101020916121101495591291050</v>
+        <v>010401010209161211014955912910520550101020109880</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
@@ -696,6 +696,9 @@
       <c r="C31" t="str">
         <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -754,7 +757,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010401010209161211014955912910520550101020109880</v>
+        <v>010401010209161211014955912910520550101020109881</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-8.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L40"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,12 +697,90 @@
         <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>4</v>
+      </c>
+      <c r="C39" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L40"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -757,7 +835,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010401010209161211014955912910520550101020109881</v>
+        <v>010401010209161211014955912910520550101020109881081048810102030</v>
       </c>
     </row>
   </sheetData>
